--- a/output/laminas_comunales/comunal_s_isapre_a_2021_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2021_o_higgins.xlsx
@@ -375,76 +375,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>Machalí</t>
         </is>
       </c>
       <c r="C2">
-        <v>45649</v>
+        <v>39.08167503681607</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Machalí</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="C3">
-        <v>20700</v>
+        <v>18.071440165002</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>Olivar</t>
         </is>
       </c>
       <c r="C4">
-        <v>9355</v>
+        <v>13.85778475144426</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Requínoa</t>
         </is>
       </c>
       <c r="C5">
-        <v>4909</v>
+        <v>12.62753778577111</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="C6">
-        <v>4482</v>
+        <v>11.78538133991786</v>
       </c>
     </row>
     <row r="7">
@@ -459,187 +459,187 @@
         </is>
       </c>
       <c r="C7">
-        <v>3833</v>
+        <v>10.92738831713088</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Requínoa</t>
+          <t>Doñihue</t>
         </is>
       </c>
       <c r="C8">
-        <v>3651</v>
+        <v>10.9070498428379</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Coinco</t>
         </is>
       </c>
       <c r="C9">
-        <v>3446</v>
+        <v>10.56096918619963</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Doñihue</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="C10">
-        <v>2429</v>
+        <v>9.407468043574083</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mostazal</t>
+          <t>Codegua</t>
         </is>
       </c>
       <c r="C11">
-        <v>2097</v>
+        <v>8.834084141406429</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Olivar</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="C12">
-        <v>1943</v>
+        <v>8.373223180658487</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chimbarongo</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="C13">
-        <v>1921</v>
+        <v>8.306150427835295</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Mostazal</t>
         </is>
       </c>
       <c r="C14">
-        <v>1757</v>
+        <v>8.059494984434451</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Las Cabras</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="C15">
-        <v>1440</v>
+        <v>7.86976177498477</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Coltauco</t>
+          <t>Navidad</t>
         </is>
       </c>
       <c r="C16">
-        <v>1331</v>
+        <v>7.454192115491393</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Codegua</t>
+          <t>Placilla</t>
         </is>
       </c>
       <c r="C17">
-        <v>1157</v>
+        <v>6.360500215610177</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>Litueche</t>
         </is>
       </c>
       <c r="C18">
-        <v>1043</v>
+        <v>6.27647285329226</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>Coltauco</t>
         </is>
       </c>
       <c r="C19">
-        <v>887</v>
+        <v>6.240330067044868</v>
       </c>
     </row>
     <row r="20">
@@ -654,217 +654,217 @@
         </is>
       </c>
       <c r="C20">
-        <v>875</v>
+        <v>6.016640308051984</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Coinco</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="C21">
-        <v>802</v>
+        <v>5.91538112522686</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Malloa</t>
+          <t>Peralillo</t>
         </is>
       </c>
       <c r="C22">
-        <v>782</v>
+        <v>5.679530201342282</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
+          <t>Marchigüe</t>
         </is>
       </c>
       <c r="C23">
-        <v>776</v>
+        <v>5.662695000614175</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Peralillo</t>
+          <t>Malloa</t>
         </is>
       </c>
       <c r="C24">
-        <v>677</v>
+        <v>5.573373244957594</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chépica</t>
+          <t>Pumanque</t>
         </is>
       </c>
       <c r="C25">
-        <v>614</v>
+        <v>5.564516129032258</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Placilla</t>
+          <t>Quinta de Tilcoco</t>
         </is>
       </c>
       <c r="C26">
-        <v>590</v>
+        <v>5.536924723510524</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Navidad</t>
+          <t>La Estrella</t>
         </is>
       </c>
       <c r="C27">
-        <v>537</v>
+        <v>5.53133514986376</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Palmilla</t>
+          <t>Las Cabras</t>
         </is>
       </c>
       <c r="C28">
-        <v>492</v>
+        <v>5.354155047406581</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Litueche</t>
+          <t>Lolol</t>
         </is>
       </c>
       <c r="C29">
-        <v>489</v>
+        <v>5.189008229878644</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Marchigüe</t>
+          <t>Chimbarongo</t>
         </is>
       </c>
       <c r="C30">
-        <v>461</v>
+        <v>5.142413534639683</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lolol</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="C31">
-        <v>372</v>
+        <v>4.416670816113131</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Paredones</t>
+          <t>Palmilla</t>
         </is>
       </c>
       <c r="C32">
-        <v>238</v>
+        <v>4.195088676671214</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pumanque</t>
+          <t>Chépica</t>
         </is>
       </c>
       <c r="C33">
-        <v>207</v>
+        <v>4.148088096203216</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>La Estrella</t>
+          <t>Paredones</t>
         </is>
       </c>
       <c r="C34">
-        <v>203</v>
+        <v>3.561807841963484</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +920,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
